--- a/data.mn/public/datasets/industrial-output-total-monthly-en.xlsx
+++ b/data.mn/public/datasets/industrial-output-total-monthly-en.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,59 +415,72 @@
   </sheetPr>
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -500,22 +501,22 @@
         <v>1171.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1355.6</v>
+        <v>1378.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1651.9</v>
+        <v>1653.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2931.3</v>
+        <v>2951.9</v>
       </c>
       <c r="I2" t="n">
-        <v>3647.1</v>
+        <v>3657.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3448.8</v>
+        <v>3494.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5120.5</v>
+        <v>5095.5</v>
       </c>
     </row>
     <row r="3">
@@ -533,22 +534,22 @@
         <v>1050.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1289.1</v>
+        <v>1305.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1300.2</v>
+        <v>1302.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2655.8</v>
+        <v>2672.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3684</v>
+        <v>3676.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3284.4</v>
+        <v>3299.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5286.1</v>
+        <v>5211.1</v>
       </c>
     </row>
     <row r="4">
@@ -566,22 +567,22 @@
         <v>1030.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1539.5</v>
+        <v>1562.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1423.1</v>
+        <v>1428.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3085</v>
+        <v>3103.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4321.3</v>
+        <v>4312.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3442</v>
+        <v>3468.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5999.6</v>
+        <v>5848.3</v>
       </c>
     </row>
     <row r="5">
@@ -599,21 +600,23 @@
         <v>955.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1449.5</v>
+        <v>1469.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1705.6</v>
+        <v>1716</v>
       </c>
       <c r="H5" t="n">
-        <v>3070.5</v>
+        <v>3091.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4390.6</v>
+        <v>4395.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4017.4</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>4030.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5570.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -630,21 +633,23 @@
         <v>1208.3</v>
       </c>
       <c r="F6" t="n">
-        <v>1675.3</v>
+        <v>1689.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1841.5</v>
+        <v>1867.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3069.5</v>
+        <v>3093.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4788.3</v>
+        <v>4807</v>
       </c>
       <c r="J6" t="n">
-        <v>4458.2</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>4476.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6597.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -661,21 +666,23 @@
         <v>1380</v>
       </c>
       <c r="F7" t="n">
-        <v>1600.8</v>
+        <v>1625.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2027.3</v>
+        <v>2054.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3108.4</v>
+        <v>3152.7</v>
       </c>
       <c r="I7" t="n">
-        <v>4689.5</v>
+        <v>4700.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3856.8</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>3869.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6994.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -692,21 +699,23 @@
         <v>1404.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1407.8</v>
+        <v>1430.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1893.5</v>
+        <v>1906.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2972.7</v>
+        <v>3006.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4091.2</v>
+        <v>4102</v>
       </c>
       <c r="J8" t="n">
-        <v>4363.7</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>4378</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7007.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -723,19 +732,19 @@
         <v>1420.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1465.3</v>
+        <v>1488.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2557.3</v>
+        <v>2563.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3770</v>
+        <v>3806</v>
       </c>
       <c r="I9" t="n">
-        <v>4067.9</v>
+        <v>4078.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4849.3</v>
+        <v>4875.6</v>
       </c>
       <c r="K9" t="inlineStr"/>
     </row>
@@ -756,19 +765,19 @@
         <v>1672.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1444.5</v>
+        <v>1457.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2573.8</v>
+        <v>2590.8</v>
       </c>
       <c r="H10" t="n">
-        <v>3716.4</v>
+        <v>3753.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4158.3</v>
+        <v>4174</v>
       </c>
       <c r="J10" t="n">
-        <v>4961.8</v>
+        <v>4984.1</v>
       </c>
       <c r="K10" t="inlineStr"/>
     </row>
@@ -789,19 +798,19 @@
         <v>1912.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1617.5</v>
+        <v>1628.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2807.8</v>
+        <v>2822.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3646.5</v>
+        <v>3686.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4536.3</v>
+        <v>4553.2</v>
       </c>
       <c r="J11" t="n">
-        <v>5284.5</v>
+        <v>5319.7</v>
       </c>
       <c r="K11" t="inlineStr"/>
     </row>
@@ -822,19 +831,19 @@
         <v>1730</v>
       </c>
       <c r="F12" t="n">
-        <v>1530.5</v>
+        <v>1537.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2624.5</v>
+        <v>2636.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3770.5</v>
+        <v>3818.7</v>
       </c>
       <c r="I12" t="n">
-        <v>4072.3</v>
+        <v>4084.6</v>
       </c>
       <c r="J12" t="n">
-        <v>5236.4</v>
+        <v>5284</v>
       </c>
       <c r="K12" t="inlineStr"/>
     </row>
@@ -855,19 +864,19 @@
         <v>1801.6</v>
       </c>
       <c r="F13" t="n">
-        <v>1542.7</v>
+        <v>1541.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2782.9</v>
+        <v>2796.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3816.7</v>
+        <v>3851.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4085.7</v>
+        <v>4102</v>
       </c>
       <c r="J13" t="n">
-        <v>5776.6</v>
+        <v>5860.7</v>
       </c>
       <c r="K13" t="inlineStr"/>
     </row>
